--- a/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/stabilization/conductor_1_coupling.xlsx
+++ b/TDD_examples/CASE_4_4C_ELECTRIC_BENCHMARK/stabilization/conductor_1_coupling.xlsx
@@ -2,18 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter_flag" sheetId="1" r:id="R788d37a3c664430e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter" sheetId="2" r:id="Rebf5e84859e74967"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_choice" sheetId="3" r:id="R70c9eca57fcf4791"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_HTC" sheetId="4" r:id="Rc917cc5f4f1942d9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="thermal_contact_resistance" sheetId="5" r:id="Rf69893fa739c49d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_multiplier" sheetId="6" r:id="Reb3f03ec60fd47e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance_mode" sheetId="7" r:id="R5976a3f34ecd4f82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance" sheetId="8" r:id="Rfe655f8310144efd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="open_perimeter_fract" sheetId="9" r:id="Rdadc6ba2acc54229"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="interf_thickness" sheetId="10" r:id="R1f88e1f39cb04ffc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trans_transp_multiplier" sheetId="11" r:id="R661ade175fcc4e26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="view_factors" sheetId="12" r:id="R335fcea4bff74561"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter_flag" sheetId="1" r:id="R4ba39f9cecb44f32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_perimeter" sheetId="2" r:id="R43a28295988c4899"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_choice" sheetId="3" r:id="R165758f223854cd1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="contact_HTC" sheetId="4" r:id="R8cb386c8f46c4fd3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="thermal_contact_resistance" sheetId="5" r:id="R8e1b3db731d4417c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HTC_multiplier" sheetId="6" r:id="R252fd12f4d564293"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance_mode" sheetId="7" r:id="R83b6ba0c92894840"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="electric_conductance" sheetId="8" r:id="R7872c926391b496d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="open_perimeter_fract" sheetId="9" r:id="R1b92c674703a46f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="interf_thickness" sheetId="10" r:id="R83913713776c4e75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="trans_transp_multiplier" sheetId="11" r:id="R38fdc7b54e7f4893"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="view_factors" sheetId="12" r:id="Rf4c82d00866e489e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1777,7 +1777,7 @@
       <x:c r="A1" s="6"/>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6" t="str">
-        <x:v>%[] flag to define the model to compute the HTC (yellow cells are those to thake into account). flag to decide how to evaluate interface htc.</x:v>
+        <x:v>%[] Flag used to select the HTC model (yellow cells are taken into account). This flag determines how the interface HTC is evaluated.</x:v>
       </x:c>
       <x:c r="D1" s="6"/>
       <x:c r="E1" s="6"/>
@@ -2943,7 +2943,7 @@
       <x:c r="A1" s="6"/>
       <x:c r="B1" s="6"/>
       <x:c r="C1" s="6" t="str">
-        <x:v>Flag to specify the kind of electric conductance: 1 conductance per unit length (the contact is along a line as for tow cilinder); 2 = actual conductance between components.</x:v>
+        <x:v>Flag used to specify the electric conductance: 1 = conductance per unit length (the contact is along a line, as for two cylinders); 2 = actual conductance between components.</x:v>
       </x:c>
       <x:c r="D1" s="6"/>
       <x:c r="E1" s="6"/>
